--- a/ExcelToDB/software.xlsx
+++ b/ExcelToDB/software.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\core-java\ExcelToDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\jdbc\ExcelToDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAF14620-B5E8-4052-9CE6-A7809F993D93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
